--- a/p6_deployment/data/spain/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/spain/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,17 +448,129 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bDmOFmNG</t>
+          <t>hO0nKEm3</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C2" t="n">
         <v>4.2</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>QyafIhIF</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>nDzACNof</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D4" t="n">
         <v>4.1</v>
       </c>
-      <c r="D2" t="n">
-        <v>1.73</v>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>hnqZAAAk</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.63</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ruUIA1G6</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>KbKTWiX8</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Eax2EqHs</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>M3h3GWnS</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.62</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/spain/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/spain/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="C3" t="n">
         <v>3.4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="4">
@@ -564,14 +564,66 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="C9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="D9" t="n">
-        <v>1.62</v>
-      </c>
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ITdtTrn2</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>E1Xs9lu2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CWcwKOO8</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/spain/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/spain/data_preparation/format_data/df_match_odds_form.xlsx
@@ -596,13 +596,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="C11" t="n">
         <v>3.4</v>
       </c>
       <c r="D11" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="12">

--- a/p6_deployment/data/spain/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/spain/data_preparation/format_data/df_match_odds_form.xlsx
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="C3" t="n">
         <v>3.4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -596,13 +596,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="C11" t="n">
         <v>3.4</v>
       </c>
       <c r="D11" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="12">
